--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.7%</t>
+          <t>-649.6%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.8%</t>
+          <t>-152.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.4%</t>
+          <t>-331.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.737812329743484</v>
+        <v>-3.765759706181788</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.219079897828722</v>
+        <v>1.207900947253401</v>
       </c>
       <c r="F1975" t="n">
         <v>0.725822068687433</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.693439198104916</v>
+        <v>-3.72138657454322</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.236692017919586</v>
+        <v>1.225513067344264</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7701952003260016</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.715919548963801</v>
+        <v>-3.743866925402104</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.222093671714622</v>
+        <v>1.210914721139301</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7701952003260016</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.668263818402745</v>
+        <v>-3.696211194841049</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.247537720966849</v>
+        <v>1.236358770391528</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8178509308870573</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.567745659903991</v>
+        <v>-3.595693036342294</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.292637357741076</v>
+        <v>1.281458407165754</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9183690893858119</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.551840330471638</v>
+        <v>-3.579787706909942</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.285754161989889</v>
+        <v>1.274575211414568</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8392564286765729</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.50700192886324</v>
+        <v>-3.534949305301544</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.307787225243877</v>
+        <v>1.296608274668555</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8437998616214424</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.526500385105248</v>
+        <v>-3.554447761543552</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.304148782378152</v>
+        <v>1.29296983180283</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7957152203415381</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.482297548019348</v>
+        <v>-3.510244924457651</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.327709519740349</v>
+        <v>1.316530569165027</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8399180574274385</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.489857213856395</v>
+        <v>-3.517804590294698</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.323095653874778</v>
+        <v>1.311916703299456</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8947214614372578</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.331565796317122</v>
+        <v>-3.359513172755426</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.437659986073526</v>
+        <v>1.426481035498205</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8947214614372578</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.123923792682646</v>
+        <v>-3.15187116912095</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51915749212157</v>
+        <v>1.507978541546248</v>
       </c>
       <c r="F1986" t="n">
         <v>1.102363465071734</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.072891699960118</v>
+        <v>-3.100839076398422</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.534518557448851</v>
+        <v>1.52333960687353</v>
       </c>
       <c r="F1987" t="n">
         <v>1.153395557794262</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.007667518832912</v>
+        <v>-3.035614895271216</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.577795633992438</v>
+        <v>1.566616683417117</v>
       </c>
       <c r="F1988" t="n">
         <v>1.218619738921468</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.970240498761779</v>
+        <v>-2.998187875200082</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.588727414320172</v>
+        <v>1.577548463744851</v>
       </c>
       <c r="F1989" t="n">
         <v>1.223871276950649</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.990352154796487</v>
+        <v>-3.018299531234791</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.581939544237529</v>
+        <v>1.570760593662208</v>
       </c>
       <c r="F1990" t="n">
         <v>1.234898621948069</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961938891696603</v>
+        <v>-2.989886268134907</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.753862620498693</v>
+        <v>1.742683669923372</v>
       </c>
       <c r="F1991" t="n">
         <v>1.17592305920164</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.887156630671591</v>
+        <v>-2.915104007109894</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.903888434126516</v>
+        <v>1.892709483551194</v>
       </c>
       <c r="F1992" t="n">
         <v>1.250705320226652</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.861072546407783</v>
+        <v>-2.889019922846086</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.906030043845898</v>
+        <v>1.894851093270576</v>
       </c>
       <c r="F1993" t="n">
         <v>1.250705320226652</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.773194633298662</v>
+        <v>-2.801142009736966</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.939374404673326</v>
+        <v>1.928195454098004</v>
       </c>
       <c r="F1994" t="n">
         <v>1.366630962650004</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.764302171905379</v>
+        <v>-2.792249548343682</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.96048579495743</v>
+        <v>1.949306844382109</v>
       </c>
       <c r="F1995" t="n">
         <v>1.366630962650004</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.932778288875256</v>
+        <v>-2.96072566531356</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884950395574063</v>
+        <v>1.873771444998742</v>
       </c>
       <c r="F1996" t="n">
         <v>1.338683126933423</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.486522096245817</v>
+        <v>-2.51446947268412</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.044722569813701</v>
+        <v>2.03354361923838</v>
       </c>
       <c r="F1997" t="n">
         <v>1.24396445726379</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.463800992562664</v>
+        <v>-2.491748369000968</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.044475033783867</v>
+        <v>2.033296083208545</v>
       </c>
       <c r="F1998" t="n">
         <v>1.24396445726379</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.593002805856707</v>
+        <v>-2.62095018229501</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.151700434317418</v>
+        <v>2.140521483742097</v>
       </c>
       <c r="F1999" t="n">
         <v>1.114762643969748</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.618877204330732</v>
+        <v>-2.646824580769036</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.178428497421455</v>
+        <v>2.167249546846133</v>
       </c>
       <c r="F2000" t="n">
         <v>1.159674252681489</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.611822514115559</v>
+        <v>-2.639769890553862</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177925729497069</v>
+        <v>2.166746778921748</v>
       </c>
       <c r="F2001" t="n">
         <v>1.166728942896663</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.584871289789071</v>
+        <v>-2.612818666227374</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.198712372872406</v>
+        <v>2.187533422297085</v>
       </c>
       <c r="F2002" t="n">
         <v>1.181609288924382</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.720824297845387</v>
+        <v>-2.748771674283691</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.328434301794839</v>
+        <v>2.317255351219518</v>
       </c>
       <c r="F2003" t="n">
         <v>1.181609288924382</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.743232415650259</v>
+        <v>-2.771179792088563</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.311587749575883</v>
+        <v>2.300408799000562</v>
       </c>
       <c r="F2004" t="n">
         <v>1.181609288924382</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.771456651227859</v>
+        <v>-2.799404027666163</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.302352054894481</v>
+        <v>2.291173104319159</v>
       </c>
       <c r="F2005" t="n">
         <v>1.19958604137569</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.780897577116389</v>
+        <v>-2.808844953554693</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.354829402260916</v>
+        <v>2.343650451685595</v>
       </c>
       <c r="F2006" t="n">
         <v>1.322013158919082</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.861118560890334</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.325632103296639</v>
       </c>
       <c r="F2007" t="n">
         <v>1.269739551583441</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-2.93744853849124</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.293211925150052</v>
       </c>
       <c r="F2008" t="n">
         <v>1.269739551583441</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.139702258815594</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.207130666623173</v>
       </c>
       <c r="F2009" t="n">
         <v>1.067485831259087</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.301270684342849</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.140937306622423</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9407029074612078</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.433571976440402</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.10109019664932</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9407029074612078</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.619440287279632</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>2.018748069096568</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7821373141412601</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.647341074389105</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>2.006111795379781</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7475403899983253</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.769867177091999</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.953865798275822</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6250142872954314</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-4.000381673277587</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.928365959392091</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3944997911098427</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.257102491272411</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>1.965989351196008</v>
       </c>
       <c r="F2016" t="n">
         <v>0.2860852169660278</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.411088909048551</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>1.973375053231192</v>
       </c>
       <c r="F2017" t="n">
         <v>0.2860852169660278</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.360567005220886</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>1.979635016882379</v>
       </c>
       <c r="F2018" t="n">
         <v>0.2860852169660278</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.61304215922861</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.890515444334703</v>
       </c>
       <c r="F2019" t="n">
         <v>0.2860852169660278</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.905937915708022</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.774567676261882</v>
       </c>
       <c r="F2020" t="n">
         <v>0.2860852169660278</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-5.09260204384283</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.70402376723528</v>
       </c>
       <c r="F2021" t="n">
         <v>0.259346246141468</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.238622730756792</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.640693345205885</v>
       </c>
       <c r="F2022" t="n">
         <v>0.250263154347611</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.330336739866377</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.766211798261095</v>
       </c>
       <c r="F2023" t="n">
         <v>0.250263154347611</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.334041022488043</v>
+        <v>-5.361988398926346</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759576723176243</v>
+        <v>1.748397772600922</v>
       </c>
       <c r="F2024" t="n">
         <v>0.2450946971031708</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.415975840756926</v>
+        <v>-5.44392321719523</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737032213437181</v>
+        <v>1.725853262861859</v>
       </c>
       <c r="F2025" t="n">
         <v>0.2351599515160906</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.517951963005333</v>
+        <v>-5.545899339443637</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.70516740299372</v>
+        <v>1.693988452418399</v>
       </c>
       <c r="F2026" t="n">
         <v>0.133183829267683</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.407945679528112</v>
+        <v>-5.435893055966416</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741322803628784</v>
+        <v>1.730143853053463</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1563884011849582</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.264886103787186</v>
+        <v>-5.292833480225489</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802796644647129</v>
+        <v>1.791617694071808</v>
       </c>
       <c r="F2028" t="n">
         <v>0.1644018277749375</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.963439378315348</v>
+        <v>-4.991386754753652</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.9306362177184</v>
+        <v>1.919457267143079</v>
       </c>
       <c r="F2029" t="n">
         <v>0.4658485532467748</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.988029622550532</v>
+        <v>-5.015976998988836</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921771297777037</v>
+        <v>1.910592347201716</v>
       </c>
       <c r="F2030" t="n">
         <v>0.4658485532467748</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.936991246544012</v>
+        <v>-4.964938622982316</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.9430295525594</v>
+        <v>1.931850601984079</v>
       </c>
       <c r="F2031" t="n">
         <v>0.4658485532467748</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.895851951677381</v>
+        <v>-4.923799328115685</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978523369380198</v>
+        <v>1.967344418804877</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5069878481134056</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.799217039658741</v>
+        <v>-4.827164416097045</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833361330311589</v>
+        <v>1.822182379736267</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6036227601320455</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.929797774189583</v>
+        <v>-4.957745150627887</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784631080573216</v>
+        <v>1.773452129997894</v>
       </c>
       <c r="F2034" t="n">
         <v>0.473042025601203</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.765301439998622</v>
+        <v>-4.793248816436925</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.834856433325683</v>
+        <v>1.823677482750361</v>
       </c>
       <c r="F2035" t="n">
         <v>0.473042025601203</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.792671372683054</v>
+        <v>-4.820618749121357</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.82309617068834</v>
+        <v>1.811917220113018</v>
       </c>
       <c r="F2036" t="n">
         <v>0.473042025601203</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.803056567572943</v>
+        <v>-4.831003944011247</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.828810871857456</v>
+        <v>1.817631921282135</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4626568307113137</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.821644726295168</v>
+        <v>-4.849592102733472</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.892212614144992</v>
+        <v>1.88103366356967</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4440686719890883</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.821943272991204</v>
+        <v>-4.849890649429508</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.888962206284876</v>
+        <v>1.877783255709554</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4440686719890883</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.721120139300776</v>
+        <v>-4.74906751573908</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.933822354700438</v>
+        <v>1.922643404125116</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4565328874734422</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.530338778548369</v>
+        <v>-4.558286154986673</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.010264152479944</v>
+        <v>1.999085201904623</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6473142482258496</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.511821924506549</v>
+        <v>-4.539769300944853</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.997507739834269</v>
+        <v>1.986328789258947</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6602443776510578</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.486628740005231</v>
+        <v>-4.514576116443535</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.042551950246855</v>
+        <v>2.031372999671533</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6854375621523762</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.474574613092268</v>
+        <v>-4.502521989530572</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.041060168913477</v>
+        <v>2.029881218338156</v>
       </c>
       <c r="F2044" t="n">
         <v>0.697491689065339</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.481197859782626</v>
+        <v>-4.50914523622093</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.04029150042147</v>
+        <v>2.029112549846149</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6908684423749807</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.378317270254033</v>
+        <v>-4.406264646692337</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.094294762110789</v>
+        <v>2.083115811535468</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7937490319035736</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.40175930943412</v>
+        <v>-4.429706685872424</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.105120616612349</v>
+        <v>2.093941666037027</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7937490319035736</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.419831817725732</v>
+        <v>-4.447779194164036</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.097891613295705</v>
+        <v>2.086712662720383</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7937490319035736</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.651005611602364</v>
+        <v>-4.678952988040668</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.965674009338518</v>
+        <v>1.954495058763197</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7937490319035736</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.619719591061909</v>
+        <v>-4.647666967500212</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.98521103655164</v>
+        <v>1.974032085976319</v>
       </c>
       <c r="F2050" t="n">
         <v>0.825035052444029</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.466694198948624</v>
+        <v>-4.494641575386928</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.145592192969858</v>
+        <v>2.134413242394537</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9780604445573131</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.495001512821895</v>
+        <v>-4.522948889260198</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.321735492328842</v>
+        <v>2.310556541753521</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9780604445573131</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.661594737935417</v>
+        <v>-4.689542114373721</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.224501153637516</v>
+        <v>2.213322203062194</v>
       </c>
       <c r="F2053" t="n">
         <v>0.8114672194437906</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.488530358553117</v>
+        <v>-4.516477734991421</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.297403308052154</v>
+        <v>2.286224357476832</v>
       </c>
       <c r="F2054" t="n">
         <v>0.8114672194437906</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.45928437809742</v>
+        <v>-4.487231754535724</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.306719755357928</v>
+        <v>2.295540804782606</v>
       </c>
       <c r="F2055" t="n">
         <v>0.8114672194437906</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.566209925975271</v>
+        <v>-4.594157302413575</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.261242775364422</v>
+        <v>2.2500638247891</v>
       </c>
       <c r="F2056" t="n">
         <v>0.7045416715659393</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983739</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.71122848448252</v>
+        <v>-4.739175860920824</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.204664154104757</v>
+        <v>2.193485203529435</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5595231130586907</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71187261496975</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.829570250267238</v>
+        <v>-4.857517626705541</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.257258687048623</v>
+        <v>2.246079736473301</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5702091516215808</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.87062667779367</v>
+        <v>3.810185178063114</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.881012794041824</v>
+        <v>-4.880229591908162</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.234467366664727</v>
+        <v>2.234780647518192</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5702091516215808</v>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.6%</t>
+          <t>-652.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-153.9%</t>
         </is>
       </c>
     </row>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.810185178063114</v>
+        <v>3.810185178063112</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.880229591908162</v>
+        <v>-4.908928049026249</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.234780647518192</v>
+        <v>2.223301264670956</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5702091516215808</v>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.810185178063112</v>
+        <v>3.810185178063113</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>116.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2059"/>
+  <dimension ref="A1:G2060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.810185178063113</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
@@ -48918,6 +48918,29 @@
       </c>
       <c r="G2059" t="n">
         <v>4.529354399568152</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="2" t="n">
+        <v>45522</v>
+      </c>
+      <c r="B2060" t="n">
+        <v>3.809897653755359</v>
+      </c>
+      <c r="C2060" t="n">
+        <v>4.285466823012043</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>-4.908928049026249</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>2.223301264670956</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>0.5702091516215808</v>
+      </c>
+      <c r="G2060" t="n">
+        <v>4.278530619998411</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073538</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.809897653755359</v>
+        <v>3.809897653755358</v>
       </c>
       <c r="C2060" t="n">
         <v>4.285466823012043</v>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>110.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-652.5%</t>
+          <t>-653.2%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-154.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.8%</t>
+          <t>-331.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-171.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-24.3%</t>
         </is>
       </c>
     </row>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.889019922846086</v>
+        <v>-2.923954192721161</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.894851093270576</v>
+        <v>1.880877385320546</v>
       </c>
       <c r="F1993" t="n">
         <v>1.250705320226652</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.801142009736966</v>
+        <v>-2.83607627961204</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.928195454098004</v>
+        <v>1.914221746147974</v>
       </c>
       <c r="F1994" t="n">
         <v>1.366630962650004</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.792249548343682</v>
+        <v>-2.827183818218757</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.949306844382109</v>
+        <v>1.935333136432079</v>
       </c>
       <c r="F1995" t="n">
         <v>1.366630962650004</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.96072566531356</v>
+        <v>-2.995659935188635</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.873771444998742</v>
+        <v>1.859797737048712</v>
       </c>
       <c r="F1996" t="n">
         <v>1.338683126933423</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.51446947268412</v>
+        <v>-2.549403742559195</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.03354361923838</v>
+        <v>2.019569911288349</v>
       </c>
       <c r="F1997" t="n">
         <v>1.24396445726379</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.491748369000968</v>
+        <v>-2.526682638876043</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.033296083208545</v>
+        <v>2.019322375258515</v>
       </c>
       <c r="F1998" t="n">
         <v>1.24396445726379</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.62095018229501</v>
+        <v>-2.655884452170085</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.140521483742097</v>
+        <v>2.126547775792067</v>
       </c>
       <c r="F1999" t="n">
         <v>1.114762643969748</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.646824580769036</v>
+        <v>-2.681758850644111</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.167249546846133</v>
+        <v>2.153275838896104</v>
       </c>
       <c r="F2000" t="n">
         <v>1.159674252681489</v>
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.639769890553862</v>
+        <v>-2.718116984483108</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.166746778921748</v>
+        <v>2.135407941350049</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.166728942896663</v>
+        <v>1.123316118842492</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.923048525195038</v>
+        <v>3.897000830762535</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.612818666227374</v>
+        <v>-2.69116576015662</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.187533422297085</v>
+        <v>2.156194584725386</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.181609288924382</v>
+        <v>1.138196464870211</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.941982886456411</v>
+        <v>3.915935192023909</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.748771674283691</v>
+        <v>-2.827118768212936</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.317255351219518</v>
+        <v>2.28591651364782</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.181609288924382</v>
+        <v>1.138196464870211</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.126086018601371</v>
+        <v>4.100038324168868</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.771179792088563</v>
+        <v>-2.849526886017808</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.300408799000562</v>
+        <v>2.269069961428864</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.181609288924382</v>
+        <v>1.138196464870211</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.118202713504364</v>
+        <v>4.092155019071861</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.799404027666163</v>
+        <v>-2.877751121595409</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.291173104319159</v>
+        <v>2.259834266747461</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.19958604137569</v>
+        <v>1.15617321732152</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.131042764524786</v>
+        <v>4.104995070092284</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.808844953554693</v>
+        <v>-2.887192047483939</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.343650451685595</v>
+        <v>2.312311614113896</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.322013158919082</v>
+        <v>1.278600334864911</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.260752752772668</v>
+        <v>4.234705058340166</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.861118560890334</v>
+        <v>-2.93946565481958</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.325632103296639</v>
+        <v>2.29429326572494</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.22632672752927</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.206231988484082</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.93744853849124</v>
+        <v>-3.015795632420486</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.293211925150052</v>
+        <v>2.261873087578353</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.22632672752927</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.204343801377857</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.139702258815594</v>
+        <v>-3.218049352744839</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.207130666623173</v>
+        <v>2.175791829051474</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.024073007204916</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.077811798786107</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.301270684342849</v>
+        <v>-3.379617778272094</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.140937306622423</v>
+        <v>2.109598469050725</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.8972900834070366</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>4.000176054717532</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.433571976440402</v>
+        <v>-3.511919070369648</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.10109019664932</v>
+        <v>2.069751359077622</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.8972900834070366</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>4.013249461583451</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.619440287279632</v>
+        <v>-3.697787381208878</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.018748069096568</v>
+        <v>1.98740923152487</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.738724490087089</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.910115302374422</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.647341074389105</v>
+        <v>-3.725688168318351</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.006111795379781</v>
+        <v>1.974772957808083</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.7041275659441542</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.887881189015663</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.769867177091999</v>
+        <v>-3.848214271021245</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.953865798275822</v>
+        <v>1.922526960704124</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.5816014632412603</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.811129971371126</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.000381673277587</v>
+        <v>-4.078728767206833</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.928365959392091</v>
+        <v>1.897027121820392</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.3510869670556716</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.739527233250276</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.257102491272411</v>
+        <v>-4.335449585201657</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.965989351196008</v>
+        <v>1.93465051362431</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2426723929118567</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.814790207765834</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.411088909048551</v>
+        <v>-4.489436002977797</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.973375053231192</v>
+        <v>1.942036215659494</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2426723929118567</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.883770476911474</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.360567005220886</v>
+        <v>-4.438914099150131</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.979635016882379</v>
+        <v>1.948296179310681</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2426723929118567</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.869821679031595</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.61304215922861</v>
+        <v>-4.691389253157856</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.890515444334703</v>
+        <v>1.859176606763005</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2426723929118567</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.881692168087009</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.905937915708022</v>
+        <v>-4.984285009637268</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.774567676261882</v>
+        <v>1.743228838690184</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2426723929118567</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.882902702605953</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.09260204384283</v>
+        <v>-5.170949137772076</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.70402376723528</v>
+        <v>1.672684929663582</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.2159334220872968</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.870981062338538</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.238622730756792</v>
+        <v>-5.316969824686038</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.640693345205885</v>
+        <v>1.609354507634187</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2068503302934399</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.860609059998414</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.330336739866377</v>
+        <v>-5.408683833795623</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.766211798261095</v>
+        <v>1.734872960689397</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2068503302934399</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.022813116697457</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.361988398926346</v>
+        <v>-5.440335492855592</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.748397772600922</v>
+        <v>1.717058935029223</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2450946971031708</v>
+        <v>0.2016818730489996</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.04060637474711</v>
+        <v>4.014558680314607</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.44392321719523</v>
+        <v>-5.522270311124475</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.725853262861859</v>
+        <v>1.694514425290161</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2351599515160906</v>
+        <v>0.1917471274619195</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044874944963353</v>
+        <v>4.01882725053085</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.545899339443637</v>
+        <v>-5.624246433372883</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.693988452418399</v>
+        <v>1.662649614846701</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.133183829267683</v>
+        <v>0.08977100521351189</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.992614910070211</v>
+        <v>3.966567215637708</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.435893055966416</v>
+        <v>-5.514240149895661</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.730143853053463</v>
+        <v>1.698805015481764</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1563884011849582</v>
+        <v>0.1129755771307871</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998690540464752</v>
+        <v>3.972642846032249</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.292833480225489</v>
+        <v>-5.371180574154735</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.791617694071808</v>
+        <v>1.76027885650011</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1644018277749375</v>
+        <v>0.1209890037207664</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007748607140713</v>
+        <v>3.98170091270821</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.991386754753652</v>
+        <v>-5.069733848682898</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.919457267143079</v>
+        <v>1.88811842957138</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4224357291926036</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.195877525306352</v>
+        <v>4.169829830873849</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.015976998988836</v>
+        <v>-5.094324092918082</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.910592347201716</v>
+        <v>1.879253509630018</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4224357291926036</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196848703059063</v>
+        <v>4.17080100862656</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.964938622982316</v>
+        <v>-5.043285716911561</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.931850601984079</v>
+        <v>1.900511764412381</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4224357291926036</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197691607438817</v>
+        <v>4.171643913006315</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.923799328115685</v>
+        <v>-5.00214642204493</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.967344418804877</v>
+        <v>1.936005581233179</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5069878481134056</v>
+        <v>0.4635750240592345</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.241413283232942</v>
+        <v>4.215365588800439</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.827164416097045</v>
+        <v>-4.90551151002629</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.822182379736267</v>
+        <v>1.790843542164569</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6036227601320455</v>
+        <v>0.5602099360778744</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.11557822656806</v>
+        <v>4.089530532135557</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.957745150627887</v>
+        <v>-5.036092244557133</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.773452129997894</v>
+        <v>1.742113292426196</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.473042025601203</v>
+        <v>0.4296292015470319</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040731829923518</v>
+        <v>4.014684135491016</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.793248816436925</v>
+        <v>-4.871595910366171</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.823677482750361</v>
+        <v>1.792338645178663</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.473042025601203</v>
+        <v>0.4296292015470319</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.025158648999601</v>
+        <v>3.999110954567098</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.820618749121357</v>
+        <v>-4.898965843050603</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.811917220113018</v>
+        <v>1.78057838254132</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.473042025601203</v>
+        <v>0.4296292015470319</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.024346359436031</v>
+        <v>3.998298665003528</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.831003944011247</v>
+        <v>-4.909351037940493</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.817631921282135</v>
+        <v>1.786293083710436</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4626568307113137</v>
+        <v>0.4192440066571426</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.027984021627169</v>
+        <v>4.001936327194667</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.849592102733472</v>
+        <v>-4.927939196662718</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.88103366356967</v>
+        <v>1.849694825997972</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4440686719890883</v>
+        <v>0.4006558479349172</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.087668132170259</v>
+        <v>4.061620437737757</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.849890649429508</v>
+        <v>-4.928237743358753</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.877783255709554</v>
+        <v>1.846444418137856</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4440686719890883</v>
+        <v>0.4006558479349172</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.084537142988558</v>
+        <v>4.058489448556055</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.74906751573908</v>
+        <v>-4.827414609668326</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.922643404125116</v>
+        <v>1.891304566553418</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4565328874734422</v>
+        <v>0.413120063419271</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.096546567218561</v>
+        <v>4.070498872786059</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.558286154986673</v>
+        <v>-4.636633248915919</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.999085201904623</v>
+        <v>1.967746364332924</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6473142482258496</v>
+        <v>0.6039014241716785</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.211144637148549</v>
+        <v>4.185096942716046</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.539769300944853</v>
+        <v>-4.618116394874098</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.986328789258947</v>
+        <v>1.954989951687249</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6602443776510578</v>
+        <v>0.6168315535968867</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198739560541271</v>
+        <v>4.172691866108768</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.514576116443535</v>
+        <v>-4.59292321037278</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.031372999671533</v>
+        <v>2.000034162099835</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6854375621523762</v>
+        <v>0.642024738098205</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.24882240785412</v>
+        <v>4.222774713421617</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.502521989530572</v>
+        <v>-4.580869083459818</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.029881218338156</v>
+        <v>1.998542380766458</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.697491689065339</v>
+        <v>0.6540788650111679</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.249741451903335</v>
+        <v>4.223693757470833</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.50914523622093</v>
+        <v>-4.587492330150176</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.029112549846149</v>
+        <v>1.99777371227445</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6908684423749807</v>
+        <v>0.6474556183208096</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.247648134073256</v>
+        <v>4.221600439640754</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.406264646692337</v>
+        <v>-4.484611740621583</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.083115811535468</v>
+        <v>2.051776973963769</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7937490319035736</v>
+        <v>0.7503362078494025</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.322227513668294</v>
+        <v>4.296179819235792</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.429706685872424</v>
+        <v>-4.50805377980167</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.093941666037027</v>
+        <v>2.062602828465329</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7937490319035736</v>
+        <v>0.7503362078494025</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.342430183841889</v>
+        <v>4.316382489409386</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.447779194164036</v>
+        <v>-4.526126288093281</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.086712662720383</v>
+        <v>2.055373825148685</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7937490319035736</v>
+        <v>0.7503362078494025</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.342430183841889</v>
+        <v>4.316382489409386</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.678952988040668</v>
+        <v>-4.757300081969913</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.954495058763197</v>
+        <v>1.923156221191499</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7937490319035736</v>
+        <v>0.7503362078494025</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.302682097435356</v>
+        <v>4.276634403002853</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.647666967500212</v>
+        <v>-4.726014061429458</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.974032085976319</v>
+        <v>1.942693248404621</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.825035052444029</v>
+        <v>0.7816222283898578</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.328476328756569</v>
+        <v>4.302428634324066</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.494641575386928</v>
+        <v>-4.572988669316174</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.134413242394537</v>
+        <v>2.103074404822838</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9780604445573131</v>
+        <v>0.934647620503142</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.519462563597443</v>
+        <v>4.49341486916494</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.522948889260198</v>
+        <v>-4.601295983189444</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.310556541753521</v>
+        <v>2.279217704181823</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9780604445573131</v>
+        <v>0.934647620503142</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.706928788505736</v>
+        <v>4.680881094073233</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.689542114373721</v>
+        <v>-4.767889208302966</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.213322203062194</v>
+        <v>2.181983365490496</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8114672194437906</v>
+        <v>0.7680543953896195</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.576375804791704</v>
+        <v>4.550328110359202</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.516477734991421</v>
+        <v>-4.594824828920666</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.286224357476832</v>
+        <v>2.254885519905134</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8114672194437906</v>
+        <v>0.7680543953896195</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.580052207453422</v>
+        <v>4.55400451302092</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.487231754535724</v>
+        <v>-4.56557884846497</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.295540804782606</v>
+        <v>2.264201967210908</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8114672194437906</v>
+        <v>0.7680543953896195</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.577670262576918</v>
+        <v>4.551622568144415</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.594157302413575</v>
+        <v>-4.672504396342821</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.2500638247891</v>
+        <v>2.218724987217402</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7045416715659393</v>
+        <v>0.6611288475117681</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.510808173007842</v>
+        <v>4.484760478575339</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.739175860920824</v>
+        <v>-4.81752295485007</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.193485203529435</v>
+        <v>2.162146365957737</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5595231130586907</v>
+        <v>0.5161102890045196</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.425225840046727</v>
+        <v>4.399178145614224</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.857517626705541</v>
+        <v>-4.935864720634787</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.246079736473301</v>
+        <v>2.214740898901603</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5702091516215808</v>
+        <v>0.5267963275674097</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.531568702442214</v>
+        <v>4.505521008009711</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073538</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.908928049026249</v>
+        <v>-4.916173907207121</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.223301264670956</v>
+        <v>2.220402921398608</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5702091516215808</v>
+        <v>0.5267963275674097</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.529354399568152</v>
+        <v>4.50330670513565</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.809897653755358</v>
+        <v>3.71265107693308</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.285466823012043</v>
+        <v>4.223826578952412</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.908928049026249</v>
+        <v>-4.916173907207121</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.223301264670956</v>
+        <v>2.220402921398608</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5702091516215808</v>
+        <v>0.5267963275674097</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.278530619998411</v>
+        <v>4.21689037593878</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>107.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.4%</t>
+          <t>430.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-653.2%</t>
+          <t>-649.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.2%</t>
+          <t>-152.8%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.0%</t>
+          <t>-330.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-171.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.765759706181788</v>
+        <v>-3.737812329743484</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.207900947253401</v>
+        <v>1.219079897828722</v>
       </c>
       <c r="F1975" t="n">
         <v>0.725822068687433</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.72138657454322</v>
+        <v>-3.693439198104916</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.225513067344264</v>
+        <v>1.236692017919586</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7701952003260016</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.743866925402104</v>
+        <v>-3.715919548963801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.210914721139301</v>
+        <v>1.222093671714622</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7701952003260016</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.696211194841049</v>
+        <v>-3.668263818402745</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.236358770391528</v>
+        <v>1.247537720966849</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8178509308870573</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.595693036342294</v>
+        <v>-3.567745659903991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.281458407165754</v>
+        <v>1.292637357741076</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9183690893858119</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.579787706909942</v>
+        <v>-3.551840330471638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.274575211414568</v>
+        <v>1.285754161989889</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8392564286765729</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.534949305301544</v>
+        <v>-3.50700192886324</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.296608274668555</v>
+        <v>1.307787225243877</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8437998616214424</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.554447761543552</v>
+        <v>-3.526500385105248</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.29296983180283</v>
+        <v>1.304148782378152</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7957152203415381</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.510244924457651</v>
+        <v>-3.482297548019348</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.316530569165027</v>
+        <v>1.327709519740349</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8399180574274385</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.517804590294698</v>
+        <v>-3.489857213856395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.311916703299456</v>
+        <v>1.323095653874778</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8947214614372578</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.359513172755426</v>
+        <v>-3.331565796317122</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.426481035498205</v>
+        <v>1.437659986073526</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8947214614372578</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.15187116912095</v>
+        <v>-3.123923792682646</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.507978541546248</v>
+        <v>1.51915749212157</v>
       </c>
       <c r="F1986" t="n">
         <v>1.102363465071734</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.100839076398422</v>
+        <v>-3.072891699960118</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.52333960687353</v>
+        <v>1.534518557448851</v>
       </c>
       <c r="F1987" t="n">
         <v>1.153395557794262</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.035614895271216</v>
+        <v>-3.007667518832912</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.566616683417117</v>
+        <v>1.577795633992438</v>
       </c>
       <c r="F1988" t="n">
         <v>1.218619738921468</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.998187875200082</v>
+        <v>-2.970240498761779</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.577548463744851</v>
+        <v>1.588727414320172</v>
       </c>
       <c r="F1989" t="n">
         <v>1.223871276950649</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.018299531234791</v>
+        <v>-2.990352154796487</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.570760593662208</v>
+        <v>1.581939544237529</v>
       </c>
       <c r="F1990" t="n">
         <v>1.234898621948069</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.989886268134907</v>
+        <v>-2.961938891696603</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.742683669923372</v>
+        <v>1.753862620498693</v>
       </c>
       <c r="F1991" t="n">
         <v>1.17592305920164</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.915104007109894</v>
+        <v>-2.887156630671591</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.892709483551194</v>
+        <v>1.903888434126516</v>
       </c>
       <c r="F1992" t="n">
         <v>1.250705320226652</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.923954192721161</v>
+        <v>-2.861072546407783</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.880877385320546</v>
+        <v>1.906030043845898</v>
       </c>
       <c r="F1993" t="n">
         <v>1.250705320226652</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.83607627961204</v>
+        <v>-2.773194633298662</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.914221746147974</v>
+        <v>1.939374404673326</v>
       </c>
       <c r="F1994" t="n">
         <v>1.366630962650004</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.827183818218757</v>
+        <v>-2.764302171905379</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.935333136432079</v>
+        <v>1.96048579495743</v>
       </c>
       <c r="F1995" t="n">
         <v>1.366630962650004</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.995659935188635</v>
+        <v>-2.932778288875256</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.859797737048712</v>
+        <v>1.884950395574063</v>
       </c>
       <c r="F1996" t="n">
         <v>1.338683126933423</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.549403742559195</v>
+        <v>-2.486522096245817</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.019569911288349</v>
+        <v>2.044722569813701</v>
       </c>
       <c r="F1997" t="n">
         <v>1.24396445726379</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.526682638876043</v>
+        <v>-2.463800992562664</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.019322375258515</v>
+        <v>2.044475033783867</v>
       </c>
       <c r="F1998" t="n">
         <v>1.24396445726379</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.655884452170085</v>
+        <v>-2.593002805856707</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.126547775792067</v>
+        <v>2.151700434317418</v>
       </c>
       <c r="F1999" t="n">
         <v>1.114762643969748</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.681758850644111</v>
+        <v>-2.618877204330732</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.153275838896104</v>
+        <v>2.178428497421455</v>
       </c>
       <c r="F2000" t="n">
         <v>1.159674252681489</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.718116984483108</v>
+        <v>-2.655663587935255</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.135407941350049</v>
+        <v>2.160389299969191</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.123316118842492</v>
+        <v>1.122887869076966</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.897000830762535</v>
+        <v>3.89674388090322</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.69116576015662</v>
+        <v>-2.628712363608767</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.156194584725386</v>
+        <v>2.181175943344527</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.138196464870211</v>
+        <v>1.137768215104685</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.915935192023909</v>
+        <v>3.915678242164593</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.827118768212936</v>
+        <v>-2.764665371665084</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.28591651364782</v>
+        <v>2.310897872266961</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.138196464870211</v>
+        <v>1.137768215104685</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.100038324168868</v>
+        <v>4.099781374309552</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.849526886017808</v>
+        <v>-2.787073489469956</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.269069961428864</v>
+        <v>2.294051320048005</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.138196464870211</v>
+        <v>1.137768215104685</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.092155019071861</v>
+        <v>4.091898069212546</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.877751121595409</v>
+        <v>-2.815297725047556</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.259834266747461</v>
+        <v>2.284815625366602</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.15617321732152</v>
+        <v>1.155744967555994</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.104995070092284</v>
+        <v>4.104738120232969</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.887192047483939</v>
+        <v>-2.824738650936086</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.312311614113896</v>
+        <v>2.337292972733038</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.278600334864911</v>
+        <v>1.278172085099385</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.234705058340166</v>
+        <v>4.234448108480851</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.93946565481958</v>
+        <v>-2.877012258271727</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.29429326572494</v>
+        <v>2.319274624344082</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.22632672752927</v>
+        <v>1.225898477763744</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.206231988484082</v>
+        <v>4.205975038624766</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.015795632420486</v>
+        <v>-2.953342235872633</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.261873087578353</v>
+        <v>2.286854446197495</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.22632672752927</v>
+        <v>1.225898477763744</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.204343801377857</v>
+        <v>4.204086851518541</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.218049352744839</v>
+        <v>-3.155595956196986</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.175791829051474</v>
+        <v>2.200773187670616</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.024073007204916</v>
+        <v>1.02364475743939</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.077811798786107</v>
+        <v>4.077554848926792</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.379617778272094</v>
+        <v>-3.317164381724242</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.109598469050725</v>
+        <v>2.134579827669866</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8972900834070366</v>
+        <v>0.8968618336415107</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.000176054717532</v>
+        <v>3.999919104858217</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.511919070369648</v>
+        <v>-3.449465673821795</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.069751359077622</v>
+        <v>2.094732717696763</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8972900834070366</v>
+        <v>0.8968618336415107</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.013249461583451</v>
+        <v>4.012992511724135</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.697787381208878</v>
+        <v>-3.635333984661025</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.98740923152487</v>
+        <v>2.012390590144011</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.738724490087089</v>
+        <v>0.738296240321563</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.910115302374422</v>
+        <v>3.909858352515106</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.725688168318351</v>
+        <v>-3.663234771770498</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.974772957808083</v>
+        <v>1.999754316427224</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7041275659441542</v>
+        <v>0.7036993161786282</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.887881189015663</v>
+        <v>3.887624239156348</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.848214271021245</v>
+        <v>-3.785760874473392</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.922526960704124</v>
+        <v>1.947508319323265</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5816014632412603</v>
+        <v>0.5811732134757344</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.811129971371126</v>
+        <v>3.81087302151181</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.078728767206833</v>
+        <v>-4.01627537065898</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.897027121820392</v>
+        <v>1.922008480439533</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3510869670556716</v>
+        <v>0.3506587172901456</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.739527233250276</v>
+        <v>3.73927028339096</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.335449585201657</v>
+        <v>-4.272996188653805</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.93465051362431</v>
+        <v>1.959631872243451</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2426723929118567</v>
+        <v>0.2422441431463308</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.814790207765834</v>
+        <v>3.814533257906519</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.489436002977797</v>
+        <v>-4.426982606429945</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.942036215659494</v>
+        <v>1.967017574278635</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2426723929118567</v>
+        <v>0.2422441431463308</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.883770476911474</v>
+        <v>3.883513527052159</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.438914099150131</v>
+        <v>-4.376460702602279</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.948296179310681</v>
+        <v>1.973277537929822</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2426723929118567</v>
+        <v>0.2422441431463308</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.869821679031595</v>
+        <v>3.869564729172279</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.691389253157856</v>
+        <v>-4.628935856610004</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.859176606763005</v>
+        <v>1.884157965382146</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2426723929118567</v>
+        <v>0.2422441431463308</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.881692168087009</v>
+        <v>3.881435218227693</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.984285009637268</v>
+        <v>-4.921831613089416</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.743228838690184</v>
+        <v>1.768210197309325</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2426723929118567</v>
+        <v>0.2422441431463308</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.882902702605953</v>
+        <v>3.882645752746637</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.170949137772076</v>
+        <v>-5.108495741224224</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.672684929663582</v>
+        <v>1.697666288282723</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2159334220872968</v>
+        <v>0.2155051723217709</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.870981062338538</v>
+        <v>3.870724112479222</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.316969824686038</v>
+        <v>-5.254516428138186</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.609354507634187</v>
+        <v>1.634335866253327</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2068503302934399</v>
+        <v>0.2064220805279139</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.860609059998414</v>
+        <v>3.860352110139098</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.408683833795623</v>
+        <v>-5.346230437247771</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.734872960689397</v>
+        <v>1.759854319308538</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2068503302934399</v>
+        <v>0.2064220805279139</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.022813116697457</v>
+        <v>4.022556166838142</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.440335492855592</v>
+        <v>-5.37788209630774</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.717058935029223</v>
+        <v>1.742040293648364</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2016818730489996</v>
+        <v>0.2012536232834737</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.014558680314607</v>
+        <v>4.014301730455291</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.522270311124475</v>
+        <v>-5.459816914576623</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.694514425290161</v>
+        <v>1.719495783909302</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1917471274619195</v>
+        <v>0.1913188776963936</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.01882725053085</v>
+        <v>4.018570300671535</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.624246433372883</v>
+        <v>-5.561793036825031</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.662649614846701</v>
+        <v>1.687630973465841</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.08977100521351189</v>
+        <v>0.08934275544798598</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.966567215637708</v>
+        <v>3.966310265778393</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.514240149895661</v>
+        <v>-5.451786753347809</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.698805015481764</v>
+        <v>1.723786374100905</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1129755771307871</v>
+        <v>0.1125473273652612</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.972642846032249</v>
+        <v>3.972385896172933</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.371180574154735</v>
+        <v>-5.308727177606883</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.76027885650011</v>
+        <v>1.78526021511925</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1209890037207664</v>
+        <v>0.1205607539552405</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.98170091270821</v>
+        <v>3.981443962848895</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.069733848682898</v>
+        <v>-5.007280452135046</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.88811842957138</v>
+        <v>1.913099788190521</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4224357291926036</v>
+        <v>0.4220074794270777</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.169829830873849</v>
+        <v>4.169572881014534</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.094324092918082</v>
+        <v>-5.03187069637023</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.879253509630018</v>
+        <v>1.904234868249158</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4224357291926036</v>
+        <v>0.4220074794270777</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.17080100862656</v>
+        <v>4.170544058767244</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.043285716911561</v>
+        <v>-4.980832320363709</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.900511764412381</v>
+        <v>1.925493123031521</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4224357291926036</v>
+        <v>0.4220074794270777</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.171643913006315</v>
+        <v>4.171386963147</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.00214642204493</v>
+        <v>-4.939693025497078</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.936005581233179</v>
+        <v>1.960986939852319</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4635750240592345</v>
+        <v>0.4631467742937085</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.215365588800439</v>
+        <v>4.215108638941123</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.90551151002629</v>
+        <v>-4.843058113478438</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.790843542164569</v>
+        <v>1.81582490078371</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5602099360778744</v>
+        <v>0.5597816863123485</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.089530532135557</v>
+        <v>4.089273582276242</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.036092244557133</v>
+        <v>-4.973638848009281</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.742113292426196</v>
+        <v>1.767094651045336</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4296292015470319</v>
+        <v>0.429200951781506</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.014684135491016</v>
+        <v>4.0144271856317</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.871595910366171</v>
+        <v>-4.809142513818319</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.792338645178663</v>
+        <v>1.817320003797804</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4296292015470319</v>
+        <v>0.429200951781506</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.999110954567098</v>
+        <v>3.998854004707782</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.898965843050603</v>
+        <v>-4.836512446502751</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.78057838254132</v>
+        <v>1.805559741160461</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4296292015470319</v>
+        <v>0.429200951781506</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.998298665003528</v>
+        <v>3.998041715144212</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.909351037940493</v>
+        <v>-4.846897641392641</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.786293083710436</v>
+        <v>1.811274442329577</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4192440066571426</v>
+        <v>0.4188157568916167</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.001936327194667</v>
+        <v>4.001679377335351</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.927939196662718</v>
+        <v>-4.865485800114866</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.849694825997972</v>
+        <v>1.874676184617112</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4006558479349172</v>
+        <v>0.4002275981693913</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.061620437737757</v>
+        <v>4.061363487878441</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.928237743358753</v>
+        <v>-4.865784346810901</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.846444418137856</v>
+        <v>1.871425776756997</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4006558479349172</v>
+        <v>0.4002275981693913</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.058489448556055</v>
+        <v>4.058232498696739</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.827414609668326</v>
+        <v>-4.764961213120474</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.891304566553418</v>
+        <v>1.916285925172559</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.413120063419271</v>
+        <v>0.4126918136537451</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.070498872786059</v>
+        <v>4.070241922926743</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.636633248915919</v>
+        <v>-4.574179852368067</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.967746364332924</v>
+        <v>1.992727722952065</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6039014241716785</v>
+        <v>0.6034731744061526</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.185096942716046</v>
+        <v>4.184839992856731</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.618116394874098</v>
+        <v>-4.555662998326246</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.954989951687249</v>
+        <v>1.97997131030639</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6168315535968867</v>
+        <v>0.6164033038313608</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.172691866108768</v>
+        <v>4.172434916249452</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.59292321037278</v>
+        <v>-4.530469813824928</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.000034162099835</v>
+        <v>2.025015520718975</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.642024738098205</v>
+        <v>0.6415964883326791</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.222774713421617</v>
+        <v>4.222517763562302</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.580869083459818</v>
+        <v>-4.518415686911966</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.998542380766458</v>
+        <v>2.023523739385598</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6540788650111679</v>
+        <v>0.6536506152456419</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.223693757470833</v>
+        <v>4.223436807611518</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.587492330150176</v>
+        <v>-4.525038933602324</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.99777371227445</v>
+        <v>2.022755070893591</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6474556183208096</v>
+        <v>0.6470273685552836</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.221600439640754</v>
+        <v>4.221343489781438</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.484611740621583</v>
+        <v>-4.422158344073731</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.051776973963769</v>
+        <v>2.07675833258291</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7503362078494025</v>
+        <v>0.7499079580838766</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.296179819235792</v>
+        <v>4.295922869376477</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.50805377980167</v>
+        <v>-4.445600383253818</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.062602828465329</v>
+        <v>2.08758418708447</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7503362078494025</v>
+        <v>0.7499079580838766</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.316382489409386</v>
+        <v>4.316125539550071</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.526126288093281</v>
+        <v>-4.463672891545429</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.055373825148685</v>
+        <v>2.080355183767825</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7503362078494025</v>
+        <v>0.7499079580838766</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.316382489409386</v>
+        <v>4.316125539550071</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.757300081969913</v>
+        <v>-4.694846685422061</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.923156221191499</v>
+        <v>1.948137579810639</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7503362078494025</v>
+        <v>0.7499079580838766</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.276634403002853</v>
+        <v>4.276377453143537</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.726014061429458</v>
+        <v>-4.663560664881606</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.942693248404621</v>
+        <v>1.967674607023761</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7816222283898578</v>
+        <v>0.7811939786243319</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.302428634324066</v>
+        <v>4.30217168446475</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.572988669316174</v>
+        <v>-4.510535272768322</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.103074404822838</v>
+        <v>2.128055763441979</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.934647620503142</v>
+        <v>0.9342193707376161</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.49341486916494</v>
+        <v>4.493157919305625</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.601295983189444</v>
+        <v>-4.538842586641592</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.279217704181823</v>
+        <v>2.304199062800963</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.934647620503142</v>
+        <v>0.9342193707376161</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.680881094073233</v>
+        <v>4.680624144213917</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.767889208302966</v>
+        <v>-4.705435811755114</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.181983365490496</v>
+        <v>2.206964724109637</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7680543953896195</v>
+        <v>0.7676261456240936</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.550328110359202</v>
+        <v>4.550071160499886</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.594824828920666</v>
+        <v>-4.532371432372814</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.254885519905134</v>
+        <v>2.279866878524275</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7680543953896195</v>
+        <v>0.7676261456240936</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.55400451302092</v>
+        <v>4.553747563161604</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.56557884846497</v>
+        <v>-4.503125451917118</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.264201967210908</v>
+        <v>2.289183325830049</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7680543953896195</v>
+        <v>0.7676261456240936</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.551622568144415</v>
+        <v>4.551365618285099</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.672504396342821</v>
+        <v>-4.610050999794969</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.218724987217402</v>
+        <v>2.243706345836543</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6611288475117681</v>
+        <v>0.6607005977462422</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.484760478575339</v>
+        <v>4.484503528716023</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.81752295485007</v>
+        <v>-4.755069558302218</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.162146365957737</v>
+        <v>2.187127724576878</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5161102890045196</v>
+        <v>0.5156820392389937</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.399178145614224</v>
+        <v>4.398921195754909</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.935864720634787</v>
+        <v>-4.873411324086935</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.214740898901603</v>
+        <v>2.239722257520744</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5267963275674097</v>
+        <v>0.5263680778018838</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.505521008009711</v>
+        <v>4.505264058150395</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.916173907207121</v>
+        <v>-4.924821746407643</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.220402921398608</v>
+        <v>2.216943785718399</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5267963275674097</v>
+        <v>0.5263680778018838</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.50330670513565</v>
+        <v>4.503049755276335</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.71265107693308</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.223826578952412</v>
+        <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.916173907207121</v>
+        <v>-4.881444805703013</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.220402921398608</v>
+        <v>2.234197690074541</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5267963275674097</v>
+        <v>0.5263680778018838</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.21689037593878</v>
+        <v>4.502952883350623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240818.xlsx
+++ b/tame_output/ON/bt/strategyON_20240818.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.5%</t>
+          <t>430.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.7%</t>
+          <t>-646.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.8%</t>
+          <t>-151.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.9%</t>
+          <t>-331.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-171.4%</t>
+          <t>-172.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.715919548963801</v>
+        <v>-3.637806643640151</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.222093671714622</v>
+        <v>1.253338833844082</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7701952003260016</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.668263818402745</v>
+        <v>-3.590150913079095</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.247537720966849</v>
+        <v>1.278782883096309</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8178509308870573</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.567745659903991</v>
+        <v>-3.489632754580341</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.292637357741076</v>
+        <v>1.323882519870536</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9183690893858119</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.551840330471638</v>
+        <v>-3.473727425147988</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.285754161989889</v>
+        <v>1.316999324119349</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8392564286765729</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.50700192886324</v>
+        <v>-3.42888902353959</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.307787225243877</v>
+        <v>1.339032387373337</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8437998616214424</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.526500385105248</v>
+        <v>-3.448387479781598</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.304148782378152</v>
+        <v>1.335393944507612</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7957152203415381</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.482297548019348</v>
+        <v>-3.404184642695698</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.327709519740349</v>
+        <v>1.358954681869809</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8399180574274385</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.489857213856395</v>
+        <v>-3.411744308532745</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.323095653874778</v>
+        <v>1.354340816004238</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8947214614372578</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.331565796317122</v>
+        <v>-3.253452890993473</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.437659986073526</v>
+        <v>1.468905148202986</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8947214614372578</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.123923792682646</v>
+        <v>-3.045810887358996</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51915749212157</v>
+        <v>1.55040265425103</v>
       </c>
       <c r="F1986" t="n">
         <v>1.102363465071734</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.072891699960118</v>
+        <v>-2.994778794636468</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.534518557448851</v>
+        <v>1.565763719578311</v>
       </c>
       <c r="F1987" t="n">
         <v>1.153395557794262</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.007667518832912</v>
+        <v>-2.929554613509262</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.577795633992438</v>
+        <v>1.609040796121898</v>
       </c>
       <c r="F1988" t="n">
         <v>1.218619738921468</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.970240498761779</v>
+        <v>-2.892127593438129</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.588727414320172</v>
+        <v>1.619972576449632</v>
       </c>
       <c r="F1989" t="n">
         <v>1.223871276950649</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.990352154796487</v>
+        <v>-2.912239249472837</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.581939544237529</v>
+        <v>1.613184706366989</v>
       </c>
       <c r="F1990" t="n">
         <v>1.234898621948069</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961938891696603</v>
+        <v>-2.883825986372953</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.753862620498693</v>
+        <v>1.785107782628153</v>
       </c>
       <c r="F1991" t="n">
         <v>1.17592305920164</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.887156630671591</v>
+        <v>-2.809043725347941</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.903888434126516</v>
+        <v>1.935133596255976</v>
       </c>
       <c r="F1992" t="n">
         <v>1.250705320226652</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.861072546407783</v>
+        <v>-2.782959641084133</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.906030043845898</v>
+        <v>1.937275205975358</v>
       </c>
       <c r="F1993" t="n">
         <v>1.250705320226652</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.773194633298662</v>
+        <v>-2.695081727975012</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.939374404673326</v>
+        <v>1.970619566802785</v>
       </c>
       <c r="F1994" t="n">
         <v>1.366630962650004</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.764302171905379</v>
+        <v>-2.686189266581729</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.96048579495743</v>
+        <v>1.99173095708689</v>
       </c>
       <c r="F1995" t="n">
         <v>1.366630962650004</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.932778288875256</v>
+        <v>-2.854665383551607</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884950395574063</v>
+        <v>1.916195557703523</v>
       </c>
       <c r="F1996" t="n">
         <v>1.338683126933423</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.486522096245817</v>
+        <v>-2.408409190922167</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.044722569813701</v>
+        <v>2.075967731943161</v>
       </c>
       <c r="F1997" t="n">
         <v>1.24396445726379</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.463800992562664</v>
+        <v>-2.385688087239014</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.044475033783867</v>
+        <v>2.075720195913326</v>
       </c>
       <c r="F1998" t="n">
         <v>1.24396445726379</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.593002805856707</v>
+        <v>-2.514889900533057</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.151700434317418</v>
+        <v>2.182945596446879</v>
       </c>
       <c r="F1999" t="n">
         <v>1.114762643969748</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.618877204330732</v>
+        <v>-2.540764299007082</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.178428497421455</v>
+        <v>2.209673659550915</v>
       </c>
       <c r="F2000" t="n">
         <v>1.159674252681489</v>
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.655663587935255</v>
+        <v>-2.533709608791909</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.160389299969191</v>
+        <v>2.209170891626529</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.122887869076966</v>
+        <v>1.166728942896663</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.89674388090322</v>
+        <v>3.923048525195038</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.628712363608767</v>
+        <v>-2.506758384465421</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.181175943344527</v>
+        <v>2.229957535001866</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.137768215104685</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.915678242164593</v>
+        <v>3.941982886456411</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.764665371665084</v>
+        <v>-2.642711392521737</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.310897872266961</v>
+        <v>2.359679463924299</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.137768215104685</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.099781374309552</v>
+        <v>4.126086018601371</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.787073489469956</v>
+        <v>-2.665119510326609</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.294051320048005</v>
+        <v>2.342832911705344</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.137768215104685</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.091898069212546</v>
+        <v>4.118202713504364</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.815297725047556</v>
+        <v>-2.69334374590421</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.284815625366602</v>
+        <v>2.333597217023941</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.155744967555994</v>
+        <v>1.19958604137569</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.104738120232969</v>
+        <v>4.131042764524786</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.824738650936086</v>
+        <v>-2.70278467179274</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.337292972733038</v>
+        <v>2.386074564390376</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.278172085099385</v>
+        <v>1.322013158919082</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.234448108480851</v>
+        <v>4.260752752772668</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.877012258271727</v>
+        <v>-2.755058279128381</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.319274624344082</v>
+        <v>2.36805621600142</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.225898477763744</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.205975038624766</v>
+        <v>4.232279682916585</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.953342235872633</v>
+        <v>-2.831388256729287</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.286854446197495</v>
+        <v>2.335636037854833</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.225898477763744</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.204086851518541</v>
+        <v>4.23039149581036</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.155595956196986</v>
+        <v>-3.03364197705364</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.200773187670616</v>
+        <v>2.249554779327954</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.02364475743939</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.077554848926792</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.317164381724242</v>
+        <v>-3.195210402580895</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.134579827669866</v>
+        <v>2.183361419327205</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8968618336415107</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.999919104858217</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.449465673821795</v>
+        <v>-3.327511694678448</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.094732717696763</v>
+        <v>2.143514309354102</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8968618336415107</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.012992511724135</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.635333984661025</v>
+        <v>-3.513380005517678</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.012390590144011</v>
+        <v>2.06117218180135</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.738296240321563</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.909858352515106</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.663234771770498</v>
+        <v>-3.541280792627151</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.999754316427224</v>
+        <v>2.048535908084562</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7036993161786282</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.887624239156348</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.785760874473392</v>
+        <v>-3.663806895330045</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.947508319323265</v>
+        <v>1.996289910980604</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5811732134757344</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.81087302151181</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.01627537065898</v>
+        <v>-3.894321391515634</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.922008480439533</v>
+        <v>1.970790072096872</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3506587172901456</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.73927028339096</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.272996188653805</v>
+        <v>-4.151042209510457</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.959631872243451</v>
+        <v>2.00841346390079</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2422441431463308</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.814533257906519</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.426982606429945</v>
+        <v>-4.305028627286598</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.967017574278635</v>
+        <v>2.015799165935973</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2422441431463308</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.883513527052159</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.376460702602279</v>
+        <v>-4.254506723458932</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.973277537929822</v>
+        <v>2.022059129587161</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2422441431463308</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.869564729172279</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.628935856610004</v>
+        <v>-4.506981877466656</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.884157965382146</v>
+        <v>1.932939557039485</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2422441431463308</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.881435218227693</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.921831613089416</v>
+        <v>-4.799877633946068</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.768210197309325</v>
+        <v>1.816991788966664</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2422441431463308</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.882645752746637</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.108495741224224</v>
+        <v>-4.986541762080877</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.697666288282723</v>
+        <v>1.746447879940062</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2155051723217709</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.870724112479222</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.254516428138186</v>
+        <v>-5.132562448994839</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.634335866253327</v>
+        <v>1.683117457910666</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2064220805279139</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.860352110139098</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.346230437247771</v>
+        <v>-5.224276458104423</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.759854319308538</v>
+        <v>1.808635910965877</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2064220805279139</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.022556166838142</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.37788209630774</v>
+        <v>-5.255928117164393</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.742040293648364</v>
+        <v>1.790821885305703</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2012536232834737</v>
+        <v>0.2450946971031708</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.014301730455291</v>
+        <v>4.04060637474711</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.459816914576623</v>
+        <v>-5.302003268781338</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.719495783909302</v>
+        <v>1.782621242227416</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1913188776963936</v>
+        <v>0.199163255558635</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.018570300671535</v>
+        <v>4.02327692738888</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.561793036825031</v>
+        <v>-5.403979391029745</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.687630973465841</v>
+        <v>1.750756431783956</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.08934275544798598</v>
+        <v>0.09718713331022738</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.966310265778393</v>
+        <v>3.971016892495737</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.451786753347809</v>
+        <v>-5.293973107552524</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.723786374100905</v>
+        <v>1.78691183241902</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1125473273652612</v>
+        <v>0.1203917052275026</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.972385896172933</v>
+        <v>3.977092522890278</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.308727177606883</v>
+        <v>-5.150913531811598</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.78526021511925</v>
+        <v>1.848385673437364</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1205607539552405</v>
+        <v>0.1284051318174819</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.981443962848895</v>
+        <v>3.98615058956624</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.007280452135046</v>
+        <v>-4.849466806339761</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.913099788190521</v>
+        <v>1.976225246508635</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4220074794270777</v>
+        <v>0.4298518572893191</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.169572881014534</v>
+        <v>4.174279507731878</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.03187069637023</v>
+        <v>-4.874057050574945</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.904234868249158</v>
+        <v>1.967360326567272</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4220074794270777</v>
+        <v>0.4298518572893191</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.170544058767244</v>
+        <v>4.175250685484589</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.980832320363709</v>
+        <v>-4.823018674568424</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.925493123031521</v>
+        <v>1.988618581349635</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4220074794270777</v>
+        <v>0.4298518572893191</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.171386963147</v>
+        <v>4.176093589864344</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.939693025497078</v>
+        <v>-4.781879379701794</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.960986939852319</v>
+        <v>2.024112398170433</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4631467742937085</v>
+        <v>0.4709911521559499</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.215108638941123</v>
+        <v>4.219815265658468</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.843058113478438</v>
+        <v>-4.685244467683154</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.81582490078371</v>
+        <v>1.878950359101824</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5597816863123485</v>
+        <v>0.5676260641745898</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.089273582276242</v>
+        <v>4.093980208993586</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.973638848009281</v>
+        <v>-4.815825202213996</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.767094651045336</v>
+        <v>1.83022010936345</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.429200951781506</v>
+        <v>0.4370453296437473</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.0144271856317</v>
+        <v>4.019133812349045</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.809142513818319</v>
+        <v>-4.651328868023034</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.817320003797804</v>
+        <v>1.880445462115918</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.429200951781506</v>
+        <v>0.4370453296437473</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998854004707782</v>
+        <v>4.003560631425128</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.836512446502751</v>
+        <v>-4.678698800707466</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.805559741160461</v>
+        <v>1.868685199478574</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.429200951781506</v>
+        <v>0.4370453296437473</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.998041715144212</v>
+        <v>4.002748341861557</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.846897641392641</v>
+        <v>-4.689083995597356</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.811274442329577</v>
+        <v>1.874399900647691</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4188157568916167</v>
+        <v>0.426660134753858</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.001679377335351</v>
+        <v>4.006386004052696</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.865485800114866</v>
+        <v>-4.707672154319581</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.874676184617112</v>
+        <v>1.937801642935226</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4002275981693913</v>
+        <v>0.4080719760316326</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.061363487878441</v>
+        <v>4.066070114595786</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.865784346810901</v>
+        <v>-4.707970701015617</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.871425776756997</v>
+        <v>1.93455123507511</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4002275981693913</v>
+        <v>0.4080719760316326</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.058232498696739</v>
+        <v>4.062939125414085</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.764961213120474</v>
+        <v>-4.607147567325189</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.916285925172559</v>
+        <v>1.979411383490673</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4126918136537451</v>
+        <v>0.4205361915159865</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.070241922926743</v>
+        <v>4.074948549644088</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.574179852368067</v>
+        <v>-4.416366206572782</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.992727722952065</v>
+        <v>2.055853181270179</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6034731744061526</v>
+        <v>0.6113175522683938</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.184839992856731</v>
+        <v>4.189546619574076</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.555662998326246</v>
+        <v>-4.397849352530962</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.97997131030639</v>
+        <v>2.043096768624504</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6164033038313608</v>
+        <v>0.624247681693602</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.172434916249452</v>
+        <v>4.177141542966798</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.530469813824928</v>
+        <v>-4.372656168029644</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.025015520718975</v>
+        <v>2.088140979037089</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6415964883326791</v>
+        <v>0.6494408661949204</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.222517763562302</v>
+        <v>4.227224390279646</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.518415686911966</v>
+        <v>-4.360602041116681</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.023523739385598</v>
+        <v>2.086649197703712</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6536506152456419</v>
+        <v>0.6614949931078832</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.223436807611518</v>
+        <v>4.228143434328862</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.525038933602324</v>
+        <v>-4.367225287807039</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.022755070893591</v>
+        <v>2.085880529211705</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6470273685552836</v>
+        <v>0.6548717464175249</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.221343489781438</v>
+        <v>4.226050116498783</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.422158344073731</v>
+        <v>-4.264344698278446</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.07675833258291</v>
+        <v>2.139883790901024</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7499079580838766</v>
+        <v>0.7577523359461178</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.295922869376477</v>
+        <v>4.300629496093821</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.445600383253818</v>
+        <v>-4.287786737458533</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.08758418708447</v>
+        <v>2.150709645402584</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7499079580838766</v>
+        <v>0.7577523359461178</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.316125539550071</v>
+        <v>4.320832166267415</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.463672891545429</v>
+        <v>-4.305859245750145</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.080355183767825</v>
+        <v>2.143480642085939</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7499079580838766</v>
+        <v>0.7577523359461178</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.316125539550071</v>
+        <v>4.320832166267415</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.694846685422061</v>
+        <v>-4.537033039626777</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.948137579810639</v>
+        <v>2.011263038128753</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7499079580838766</v>
+        <v>0.7577523359461178</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.276377453143537</v>
+        <v>4.281084079860882</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.663560664881606</v>
+        <v>-4.505747019086321</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.967674607023761</v>
+        <v>2.030800065341875</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7811939786243319</v>
+        <v>0.7890383564865732</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.30217168446475</v>
+        <v>4.306878311182095</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.510535272768322</v>
+        <v>-4.352721626973037</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.128055763441979</v>
+        <v>2.191181221760093</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9342193707376161</v>
+        <v>0.9420637485998573</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.493157919305625</v>
+        <v>4.49786454602297</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.538842586641592</v>
+        <v>-4.381028940846307</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.304199062800963</v>
+        <v>2.367324521119078</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9342193707376161</v>
+        <v>0.9420637485998573</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.680624144213917</v>
+        <v>4.685330770931262</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.705435811755114</v>
+        <v>-4.547622165959829</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.206964724109637</v>
+        <v>2.270090182427751</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7676261456240936</v>
+        <v>0.7754705234863348</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.550071160499886</v>
+        <v>4.554777787217231</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.532371432372814</v>
+        <v>-4.37455778657753</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.279866878524275</v>
+        <v>2.342992336842388</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7676261456240936</v>
+        <v>0.7754705234863348</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.553747563161604</v>
+        <v>4.558454189878948</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682208</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.503125451917118</v>
+        <v>-4.345311806121833</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.289183325830049</v>
+        <v>2.352308784148162</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7676261456240936</v>
+        <v>0.7754705234863348</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.551365618285099</v>
+        <v>4.556072245002444</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539111</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.610050999794969</v>
+        <v>-4.452237353999684</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.243706345836543</v>
+        <v>2.306831804154657</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6607005977462422</v>
+        <v>0.6685449756084835</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.484503528716023</v>
+        <v>4.489210155433368</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983741</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.755069558302218</v>
+        <v>-4.597255912506933</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.187127724576878</v>
+        <v>2.250253182894991</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5156820392389937</v>
+        <v>0.5235264171012349</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.398921195754909</v>
+        <v>4.403627822472253</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969752</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.873411324086935</v>
+        <v>-4.71559767829165</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.239722257520744</v>
+        <v>2.302847715838857</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5263680778018838</v>
+        <v>0.534212455664125</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.505264058150395</v>
+        <v>4.50997068486774</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073542</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.924821746407643</v>
+        <v>-4.767008100612358</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.216943785718399</v>
+        <v>2.280069244036513</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5263680778018838</v>
+        <v>0.534212455664125</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.503049755276335</v>
+        <v>4.507756381993679</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.71265107693308</v>
+        <v>3.826103787457523</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.881444805703013</v>
+        <v>-4.844241732525152</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.234197690074541</v>
+        <v>2.249078919345685</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5263680778018838</v>
+        <v>0.5122749428750957</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.502952883350623</v>
+        <v>4.494497002394551</v>
       </c>
     </row>
   </sheetData>
